--- a/OUTPUT/reverse_P0CAW8_Caulobacter_crescentus_CB15.xlsx
+++ b/OUTPUT/reverse_P0CAW8_Caulobacter_crescentus_CB15.xlsx
@@ -482,11 +482,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AAT</t>
+          <t>TAA</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0202</v>
+        <v>0.02039184326269492</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +506,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>CG</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.8682</v>
+        <v>0.8680527788884447</v>
       </c>
     </row>
   </sheetData>
